--- a/analysis/coding_worksheets/決策群組_#301.xlsx
+++ b/analysis/coding_worksheets/決策群組_#301.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,145 +451,150 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt2</t>
         </is>
@@ -618,17 +623,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -705,6 +712,9 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,17 +741,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>我選 Amy</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -818,6 +830,9 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>我選 Sally</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -931,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,17 +977,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>我選Nancy是因為，她的經歷很完整，有證券分析師，也有擔任多項基礎職務，最重要的事會計師資格，可以避免在財務長的位置被假帳糊弄，更能有效率決策</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1044,6 +1066,9 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,17 +1095,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>機密資料顯示我們可以留到下一輪討論</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1157,6 +1184,9 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,17 +1213,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>其實我在Amy和Nancy之間猶豫，如果先以履歷而言，Amy有18年的科技財務部門經驗，感覺他對這個公司的財務狀況會有深入的了解</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1270,6 +1302,9 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1296,17 +1331,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>我選sally 是因為從競爭對手公司的角度來看或許能更了解及看清楚目前公司的內部問題，加上擔任多項管理職務。</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1383,6 +1420,9 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1409,17 +1449,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>另外兩位的履歷都比較單薄一點，sally的特殊備註是在競爭對手公司擔任多項管理職務，根據競爭禁止的原則，她可能是臥底XDD不太放心讓她擔任財務長的職務</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1496,6 +1538,9 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1522,17 +1567,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>這輪來討論機密資料吧，等我打字一下～</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1609,6 +1656,9 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,17 +1685,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>在大家分享的過程中，針對候選人的合作特質或領導風格，似乎還沒有太多具體討論。有沒有人對於這部分有更多資訊或觀察可以提出嗎？</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1722,6 +1774,9 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1748,18 +1803,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>在機密資料的個人特質中，三個人各有一個「特別」的特質，分別是「不是」鼓舞人心的演講者(amy)、「善於利用組織政治為自己謀利」(sally)、「不」記得表揚他人的貢獻(nancy)
 這是我對三個人覺得有疑慮的部分</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1836,6 +1893,9 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1862,19 +1922,21 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Nancy： 注重細節和嚴格公平的要求下屬，完成公司提供的領導課程，缺點是忘記表揚他人的專案貢獻
 Sally：演講專家，人際交往被抱怨過於霸道啊，擔任公司募捐活動主席，在倫敦財務部工作過
 Amy：開會遲到、關於財務相關的資料幾乎沒提及</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1951,6 +2013,9 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1977,17 +2042,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>人格特質中Amy,sally 兩位都是注重細節，但是被員工抱怨冷漠疏遠，而Nancy不記得表揚他人的貢獻，但sally 是一位優秀的公開演講者</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -2064,6 +2131,9 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2090,18 +2160,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>我對Amy的疑慮是基礎資料過於單薄， Sally疑慮是霸道交際，財務長的身份需要跟不同部門有效溝通互動，喬事情討論收購等等，人際交往如果是霸道或背景不足恐怕難以應付
 至於Nancy不記得表揚貢獻這點，其實是最好改進的，適當提醒跟建立貢獻回報表揚機制就能解決了，畢竟她完整上過領導課程</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -2178,6 +2250,9 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2204,17 +2279,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -2291,6 +2368,9 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,17 +2397,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2404,6 +2486,9 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2430,10 +2515,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>優點的部分
 從Amy注重細節、喜歡下西洋棋的特質來看，他讓我覺得是一個擅長佈局的人，擔任爭議委員會主席的時候獲得良好評價，如果有財務糾紛或問題的時候也許會是不錯的溝通管道（補充：開會遲到這部分我的資料沒有提到）；
@@ -2441,9 +2531,6 @@
 Nancy對於如何改進內部審計實務上發表過大量的文章，對於財務的佈局也有相當的能力</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2520,6 +2607,9 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2546,17 +2636,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2633,6 +2725,9 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2659,17 +2754,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>我們的履歷資料是依樣的嗎～因為我看amy曾擔任會計事務所的分析師</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -2746,6 +2843,9 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2772,17 +2872,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>大家針對候選人的財務專業與個人特質都有不少分享，不過關於他們的國際視野或跨文化經驗，似乎還沒有被充分討論。有沒有人持有相關資訊或想法，可以補充這一塊嗎？</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -2859,6 +2961,9 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2885,17 +2990,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>我也覺得待過競爭公司的Sally有很大疑慮，是不是能夠先把他排除，從剩下兩個人來選擇？</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -2972,6 +3079,9 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2998,17 +3108,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>是一樣的，單薄是指西洋棋跟攝影比賽，感覺特質跟財務金融比較沒有關係</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -3085,6 +3197,9 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3111,17 +3226,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>個人是覺得沒有很大的問題～但如果兩位都有疑慮的話可以先暫時剔除</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -3198,6 +3315,9 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3224,17 +3344,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>我是在機密資料的部分呈現</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -3311,6 +3433,9 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3337,17 +3462,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>因為履歷上感覺Ａ和Ｎ的經歷類似</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -3424,6 +3551,9 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3450,17 +3580,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>補充：我的資料沒有提到Nancy對內部審計有改革的文章，如果有實際改革的思考，加上會計師經驗，應該能蠻好勝任財務長工作喔～</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -3537,6 +3669,9 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3563,17 +3698,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>大家針對專業經歷和個人特質已經有深入的討論，那麼在領導與合作能力方面，三位候選人是否有具體行動或表現可以分享？有沒有人有相關觀察或資訊呢？</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
@@ -3650,6 +3787,9 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3676,17 +3816,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>我覺得主要是因為ＸＸ公司的員工説他會以組織政治為自己謀利</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3763,6 +3905,9 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3789,17 +3934,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>兩位中要選的話我會選Nancy ，因為公司目前內部已有分裂問題，以個人特質來說amy 因為有冷漠抱怨的部分可能不太適合領導大家</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -3876,6 +4023,9 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3902,10 +4052,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>具體行動方面
 Amy：攝影比賽冠軍+西洋棋
@@ -3913,9 +4068,6 @@
 為了公司利益怎麼看都是選Nancy～忘記表揚貢獻可以適當改進</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
@@ -3992,6 +4144,9 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4018,17 +4173,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>在組織政治的部分，Ｎ對組織政治有良好的洞察力，如果他在財務部門中能夠善用組織權力和每個員工的特質，也許會是財務部們中不錯的領導者，再調整表揚他人貢獻的部分就更好了！！</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -4105,6 +4262,9 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4131,17 +4291,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>好耶，看來我們有共識了XD</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -4218,6 +4380,9 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4244,17 +4409,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>如果有其中一份資料提到他冷漠抱怨的態度，那讀的確不適合擔任目前公司領導者的角色</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -4331,6 +4498,9 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4357,17 +4527,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>大家已經針對候選人的專業經歷、個人特質及領導能力討論得很細緻，想再確認一下，有沒有人手上有更多關於他們國際視野或跨文化合作經驗的資訊？這部分目前好像還沒充分被討論喔！</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -4444,6 +4616,9 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4470,17 +4645,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>這部分是履歷已經討論了</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
@@ -4557,6 +4734,9 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4583,17 +4763,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
@@ -4670,6 +4852,9 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4696,17 +4881,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
@@ -4783,6 +4970,9 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4809,17 +4999,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
@@ -4896,6 +5088,9 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4922,17 +5117,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
@@ -5009,6 +5206,9 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5035,17 +5235,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
@@ -5122,6 +5324,9 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5148,17 +5353,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
@@ -5235,6 +5442,9 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
         <v>0</v>
       </c>
     </row>
